--- a/testdata/Ex.xlsx
+++ b/testdata/Ex.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Go\goxlsx\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BA74FF-B778-407E-9A65-8894C212FC1B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5000AE0-7552-4C4D-80B4-13BBEFE477A3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>тест</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>цукцук321</t>
+  </si>
+  <si>
+    <t>USO.KC</t>
   </si>
 </sst>
 </file>
@@ -85,8 +88,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -400,75 +409,90 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD476B10-AF56-44B5-A644-C541EB0B23D0}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B1">
         <v>1</v>
       </c>
-      <c r="B1">
+      <c r="C1">
         <v>2</v>
       </c>
-      <c r="C1">
+      <c r="D1" s="2">
         <v>3</v>
       </c>
-      <c r="D1">
+      <c r="E1">
         <v>4</v>
       </c>
-      <c r="E1">
+      <c r="F1">
         <v>5</v>
       </c>
-      <c r="F1">
+      <c r="G1">
         <v>6</v>
       </c>
-      <c r="G1">
+      <c r="H1">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="str">
+      <c r="C2" t="str">
         <f>OIP!C1</f>
         <v>теск</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A8"/>
+    <mergeCell ref="D1:D3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>